--- a/data/trans_orig/P36BPD02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023</t>
+          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023 (tasa de respuesta: 96,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>55887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42313</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58773</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>88434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232247</t>
+          <t>232298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263121</t>
+          <t>263652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>220944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>241793</t>
+          <t>242247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>461519</t>
+          <t>463075</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498108</t>
+          <t>499088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>56801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98008</t>
+          <t>99309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70661</t>
+          <t>70764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100038</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136117</t>
+          <t>136990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191044</t>
+          <t>190054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>209113</t>
+          <t>206841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>263972</t>
+          <t>260332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207680</t>
+          <t>207724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246712</t>
+          <t>245671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>427100</t>
+          <t>426672</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495433</t>
+          <t>494403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112681</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>163371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135673</t>
+          <t>137452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170300</t>
+          <t>172000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257030</t>
+          <t>260752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318607</t>
+          <t>321541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>55749</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74394</t>
+          <t>74687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>84350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120600</t>
+          <t>120016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85112</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118019</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94733</t>
+          <t>94416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161350</t>
+          <t>161348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205579</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154385</t>
+          <t>151708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189758</t>
+          <t>188669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189575</t>
+          <t>189640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219022</t>
+          <t>220355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>352073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401148</t>
+          <t>402470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71054</t>
+          <t>72653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105472</t>
+          <t>107786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93279</t>
+          <t>93500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214962</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177494</t>
+          <t>173904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305210</t>
+          <t>308875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121215</t>
+          <t>120183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156417</t>
+          <t>157702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183898</t>
+          <t>188466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313235</t>
+          <t>313470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323443</t>
+          <t>316804</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>460479</t>
+          <t>462931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120626</t>
+          <t>119786</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140259</t>
+          <t>140557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142453</t>
+          <t>141883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160246</t>
+          <t>160167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>269959</t>
+          <t>267703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296043</t>
+          <t>294983</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44900</t>
+          <t>45410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>70476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93911</t>
+          <t>96231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>76820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102062</t>
+          <t>100947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>114600</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149793</t>
+          <t>151380</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109673</t>
+          <t>110216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140996</t>
+          <t>140703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105936</t>
+          <t>105695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130953</t>
+          <t>131287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222548</t>
+          <t>223991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>261938</t>
+          <t>262744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84140</t>
+          <t>86408</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114983</t>
+          <t>114895</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>41346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59930</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132043</t>
+          <t>130893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167003</t>
+          <t>167428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>102277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>93899</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78823</t>
+          <t>86227</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174708</t>
+          <t>172782</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>258160</t>
+          <t>255841</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>315573</t>
+          <t>315840</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,82 +3594,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>42,69%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>332949</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>153518</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>448223</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>39,75%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>53,52%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>619008</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>387655</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>735714</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>43,08%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>52,66%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>332949</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>162230</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>451398</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>39,75%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>619008</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>383930</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>737159</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>215612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>270844</t>
+          <t>268573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>300786</t>
+          <t>302869</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>640057</t>
+          <t>653581</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>540733</t>
+          <t>544649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>966818</t>
+          <t>961043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70263</t>
+          <t>75195</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>226690</t>
+          <t>228623</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>126933</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>163385</t>
+          <t>161486</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>186579</t>
+          <t>187354</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>365917</t>
+          <t>364682</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>180236</t>
+          <t>192073</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>564092</t>
+          <t>564505</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>405369</t>
+          <t>404606</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>450805</t>
+          <t>451156</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>513480</t>
+          <t>524982</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>994466</t>
+          <t>997941</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>144012</t>
+          <t>142387</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>665624</t>
+          <t>661857</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121017</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>160432</t>
+          <t>160094</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284044</t>
+          <t>283807</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>923655</t>
+          <t>927592</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>331562</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>500955</t>
+          <t>496845</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>402364</t>
+          <t>396161</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>544077</t>
+          <t>549400</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>812749</t>
+          <t>796082</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1010541</t>
+          <t>1017847</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1092043</t>
+          <t>1059384</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1552674</t>
+          <t>1546941</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1255156</t>
+          <t>1207835</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1662853</t>
+          <t>1667796</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2547836</t>
+          <t>2531860</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3162104</t>
+          <t>3151034</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1253722</t>
+          <t>1260347</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1846244</t>
+          <t>1879156</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1336762</t>
+          <t>1329386</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1880700</t>
+          <t>1927753</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2661458</t>
+          <t>2666294</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3471391</t>
+          <t>3458948</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31442</t>
+          <t>43318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>66889</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36137</t>
+          <t>53209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>80888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41037</t>
+          <t>38137</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32384</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>47547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>73306</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>60316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88434</t>
+          <t>90063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248854</t>
+          <t>248813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232298</t>
+          <t>233570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263652</t>
+          <t>261753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>231896</t>
+          <t>245898</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>220944</t>
+          <t>231664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242247</t>
+          <t>257358</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>480749</t>
+          <t>494711</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>463075</t>
+          <t>474984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>499088</t>
+          <t>512893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75522</t>
+          <t>74645</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56801</t>
+          <t>56920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99309</t>
+          <t>95295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84969</t>
+          <t>87493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100707</t>
+          <t>104310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>160491</t>
+          <t>162139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136990</t>
+          <t>137443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190054</t>
+          <t>190363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234522</t>
+          <t>247879</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206841</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>260332</t>
+          <t>274740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>227257</t>
+          <t>247117</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207724</t>
+          <t>227591</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>245671</t>
+          <t>268598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>461779</t>
+          <t>494996</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>426672</t>
+          <t>457645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>494403</t>
+          <t>528450</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>138253</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113248</t>
+          <t>112676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163371</t>
+          <t>163838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>151986</t>
+          <t>159562</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137452</t>
+          <t>141114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172000</t>
+          <t>177443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>288257</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260752</t>
+          <t>268989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321541</t>
+          <t>327886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>446315</t>
+          <t>460778</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446315</t>
+          <t>460778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446315</t>
+          <t>460778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>464212</t>
+          <t>494172</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464212</t>
+          <t>494172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>464212</t>
+          <t>494172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>910527</t>
+          <t>954949</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>910527</t>
+          <t>954949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>910527</t>
+          <t>954949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41197</t>
+          <t>46296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>52131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74687</t>
+          <t>79030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>110622</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84350</t>
+          <t>93493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120016</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>101252</t>
+          <t>99238</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119784</t>
+          <t>114695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,27 +1785,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>82967</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68629</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94416</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>182205</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161348</t>
+          <t>162666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203357</t>
+          <t>203294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>171973</t>
+          <t>168924</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151708</t>
+          <t>151263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188669</t>
+          <t>186603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>206288</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189640</t>
+          <t>190713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220355</t>
+          <t>222128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>376397</t>
+          <t>375212</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>352073</t>
+          <t>352489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402470</t>
+          <t>399354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>314422</t>
+          <t>314458</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>314422</t>
+          <t>314458</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>314422</t>
+          <t>314458</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>346417</t>
+          <t>353581</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>346417</t>
+          <t>353581</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>346417</t>
+          <t>353581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>660840</t>
+          <t>668039</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>660840</t>
+          <t>668039</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>660840</t>
+          <t>668039</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52880</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87703</t>
+          <t>97682</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72653</t>
+          <t>79636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107786</t>
+          <t>117017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>157738</t>
+          <t>139896</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93500</t>
+          <t>123150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212753</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>245441</t>
+          <t>237577</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173904</t>
+          <t>213006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308875</t>
+          <t>268133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>139907</t>
+          <t>169464</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157702</t>
+          <t>189758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>239410</t>
+          <t>189566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>188466</t>
+          <t>171309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313470</t>
+          <t>207616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>379317</t>
+          <t>359030</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316804</t>
+          <t>326738</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>462931</t>
+          <t>382698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>244357</t>
+          <t>288517</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>244357</t>
+          <t>288517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244357</t>
+          <t>288517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>415523</t>
+          <t>352152</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>415523</t>
+          <t>352152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>415523</t>
+          <t>352152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>659879</t>
+          <t>640669</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>659879</t>
+          <t>640669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>659879</t>
+          <t>640669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130968</t>
+          <t>148314</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119786</t>
+          <t>136527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140557</t>
+          <t>159394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>151649</t>
+          <t>165877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141883</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160167</t>
+          <t>174052</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>282618</t>
+          <t>314191</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>267703</t>
+          <t>299774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>294983</t>
+          <t>328030</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35503</t>
+          <t>38683</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>49602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>61385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>82507</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70476</t>
+          <t>77842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96231</t>
+          <t>102778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178142</t>
+          <t>205030</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178142</t>
+          <t>205030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178142</t>
+          <t>205030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205089</t>
+          <t>224690</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205089</t>
+          <t>224690</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205089</t>
+          <t>224690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>383231</t>
+          <t>429720</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>383231</t>
+          <t>429720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>383231</t>
+          <t>429720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44140</t>
+          <t>50450</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>64021</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>88116</t>
+          <t>91881</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76820</t>
+          <t>79656</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100947</t>
+          <t>105609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>132256</t>
+          <t>142331</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114600</t>
+          <t>123946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>151380</t>
+          <t>162254</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>125059</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110216</t>
+          <t>107502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140703</t>
+          <t>138373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,22 +3153,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>120861</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105695</t>
+          <t>108467</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131287</t>
+          <t>133615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>243191</t>
+          <t>243050</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223991</t>
+          <t>225765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>262744</t>
+          <t>263226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>99114</t>
+          <t>96789</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86408</t>
+          <t>83354</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114895</t>
+          <t>111382</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50442</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41346</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61499</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>149366</t>
+          <t>147231</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130893</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167428</t>
+          <t>165824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>269428</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>269428</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>269428</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>256500</t>
+          <t>263184</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>256500</t>
+          <t>263184</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256500</t>
+          <t>263184</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>524813</t>
+          <t>532612</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>524813</t>
+          <t>532612</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>524813</t>
+          <t>532612</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>71230</t>
+          <t>85729</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54369</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102277</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>88526</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93899</t>
+          <t>107829</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>136253</t>
+          <t>174254</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86227</t>
+          <t>150357</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>172782</t>
+          <t>204627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>286059</t>
+          <t>328846</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>255841</t>
+          <t>297217</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>315840</t>
+          <t>356728</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>332949</t>
+          <t>391048</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>153518</t>
+          <t>366532</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>448223</t>
+          <t>417113</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>619008</t>
+          <t>719895</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>387655</t>
+          <t>680562</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>735714</t>
+          <t>756082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>275183</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>215612</t>
+          <t>247430</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>268573</t>
+          <t>305514</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>439577</t>
+          <t>277707</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>302869</t>
+          <t>254401</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>653581</t>
+          <t>302325</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>681564</t>
+          <t>552891</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>544649</t>
+          <t>517658</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>961043</t>
+          <t>592165</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>599277</t>
+          <t>689758</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>599277</t>
+          <t>689758</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>599277</t>
+          <t>689758</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>837548</t>
+          <t>757281</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>837548</t>
+          <t>757281</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>837548</t>
+          <t>757281</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1436824</t>
+          <t>1447040</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1436824</t>
+          <t>1447040</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1436824</t>
+          <t>1447040</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>159138</t>
+          <t>199528</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>175663</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>228623</t>
+          <t>228012</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>143874</t>
+          <t>176372</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>156048</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>161486</t>
+          <t>197842</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>303012</t>
+          <t>375900</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>187354</t>
+          <t>343091</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>364682</t>
+          <t>411215</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>407824</t>
+          <t>464526</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>192073</t>
+          <t>434407</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>564505</t>
+          <t>492146</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>429482</t>
+          <t>495545</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>404606</t>
+          <t>471893</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>451156</t>
+          <t>521511</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>837305</t>
+          <t>960072</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>524982</t>
+          <t>916853</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>997941</t>
+          <t>998737</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>355378</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>142387</t>
+          <t>105116</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>661857</t>
+          <t>147564</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>138556</t>
+          <t>152849</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>119284</t>
+          <t>133281</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>160094</t>
+          <t>173213</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>493935</t>
+          <t>279748</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>283807</t>
+          <t>250813</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>927592</t>
+          <t>312757</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>922340</t>
+          <t>790953</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>922340</t>
+          <t>790953</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>922340</t>
+          <t>790953</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>711912</t>
+          <t>824767</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>711912</t>
+          <t>824767</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>711912</t>
+          <t>824767</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1634252</t>
+          <t>1615720</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1634252</t>
+          <t>1615720</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1634252</t>
+          <t>1615720</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>441198</t>
+          <t>527947</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>331562</t>
+          <t>480993</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>496845</t>
+          <t>572113</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>492494</t>
+          <t>574695</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>396161</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>549400</t>
+          <t>612870</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>933691</t>
+          <t>1102642</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>796082</t>
+          <t>1044692</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1017847</t>
+          <t>1158614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1414425</t>
+          <t>1546811</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1059384</t>
+          <t>1483131</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1546941</t>
+          <t>1612345</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1531237</t>
+          <t>1678480</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1207835</t>
+          <t>1625840</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1667796</t>
+          <t>1734171</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2945662</t>
+          <t>3225291</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2531860</t>
+          <t>3142902</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3151034</t>
+          <t>3306702</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1428987</t>
+          <t>1263009</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1260347</t>
+          <t>1195506</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1879156</t>
+          <t>1324237</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1503105</t>
+          <t>1332713</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1329386</t>
+          <t>1273930</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1927753</t>
+          <t>1380520</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2932092</t>
+          <t>2595722</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2666294</t>
+          <t>2515535</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3458948</t>
+          <t>2678539</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
